--- a/doc/WW70-V2/Stueckliste-WW70-V2.xlsx
+++ b/doc/WW70-V2/Stueckliste-WW70-V2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
   <si>
     <t xml:space="preserve">Pos</t>
   </si>
@@ -154,21 +154,33 @@
     <t xml:space="preserve">Elektronik/Sensorik</t>
   </si>
   <si>
-    <t xml:space="preserve">Schütz DIL 12MC</t>
+    <t xml:space="preserve">Schütz DILM12-10</t>
   </si>
   <si>
     <t xml:space="preserve">Eaton </t>
   </si>
   <si>
+    <t xml:space="preserve">12A, 220V Ansteuerung,  ein Schliesser Kontakt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Steuertrafo 24Vdc</t>
   </si>
   <si>
-    <t xml:space="preserve">Motorschutzschalter PKZMO-10</t>
+    <t xml:space="preserve">24 Volt DC, 2 A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorschutzschalter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKZM0-16 XTPR016BC1, 16A 1 Steuerkontakt</t>
   </si>
   <si>
     <t xml:space="preserve">Relais</t>
   </si>
   <si>
+    <t xml:space="preserve">24 Volt Ansteuerung</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sicherungsautomat B6</t>
   </si>
   <si>
@@ -196,6 +208,12 @@
     <t xml:space="preserve">Magnetventil für Quellwasser</t>
   </si>
   <si>
+    <t xml:space="preserve">Not-Aus Schalter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein-Taster</t>
+  </si>
+  <si>
     <t xml:space="preserve">Klemmen</t>
   </si>
   <si>
@@ -211,7 +229,7 @@
     <t xml:space="preserve">Kabelkanal</t>
   </si>
   <si>
-    <t xml:space="preserve">DIN_Schienen</t>
+    <t xml:space="preserve">Hutschienen</t>
   </si>
   <si>
     <t xml:space="preserve">Steuerung UVR16x2</t>
@@ -236,6 +254,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -257,6 +276,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -432,16 +452,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H56"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="41.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.07"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="0" width="1.15"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="2" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="39.7"/>
   </cols>
   <sheetData>
@@ -806,7 +826,7 @@
         <v>45</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -814,10 +834,13 @@
         <v>42</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>15</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -825,13 +848,16 @@
         <v>43</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>15</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>45</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -842,10 +868,13 @@
         <v>2</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>15</v>
+      </c>
+      <c r="H38" s="0" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -853,7 +882,7 @@
         <v>45</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>15</v>
@@ -864,13 +893,13 @@
         <v>46</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>15</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -881,7 +910,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>22</v>
@@ -892,7 +921,7 @@
         <v>48</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>22</v>
@@ -903,7 +932,7 @@
         <v>49</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>22</v>
@@ -914,7 +943,7 @@
         <v>50</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>22</v>
@@ -925,7 +954,7 @@
         <v>51</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>22</v>
@@ -936,7 +965,7 @@
         <v>52</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>22</v>
@@ -946,16 +975,16 @@
       <c r="B47" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="D47" s="0" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="n">
         <v>54</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -963,7 +992,7 @@
         <v>55</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>22</v>
@@ -974,7 +1003,7 @@
         <v>56</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>22</v>
@@ -985,7 +1014,7 @@
         <v>57</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>22</v>
@@ -996,7 +1025,7 @@
         <v>58</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>22</v>
@@ -1007,7 +1036,7 @@
         <v>59</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>22</v>
@@ -1017,22 +1046,28 @@
       <c r="B54" s="1" t="n">
         <v>60</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="D55" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="H55" s="0" t="s">
-        <v>66</v>
+      <c r="D54" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
